--- a/Backtest/12-03-21/S&P500stock_12-03-21period252RS90.xlsx
+++ b/Backtest/12-03-21/S&P500stock_12-03-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
   <si>
     <t>Stock</t>
   </si>
@@ -127,142 +127,202 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>DOW</t>
-  </si>
-  <si>
-    <t>FCX</t>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>BLDR</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>NWSA</t>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>POOL</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>SPG</t>
   </si>
   <si>
     <t>AMAT</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>MOS</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>EQT</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>inf</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-05-03</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-05-05</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
+    <t>FITB</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>2022-01-26</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
+    <t>2022-02-03</t>
+  </si>
+  <si>
+    <t>2022-03-01</t>
+  </si>
+  <si>
+    <t>2022-02-07</t>
+  </si>
+  <si>
+    <t>2022-02-28</t>
+  </si>
+  <si>
+    <t>2022-02-17</t>
+  </si>
+  <si>
+    <t>2022-02-16</t>
+  </si>
+  <si>
+    <t>2022-02-23</t>
+  </si>
+  <si>
+    <t>2022-02-09</t>
+  </si>
+  <si>
+    <t>2022-02-02</t>
+  </si>
+  <si>
+    <t>2022-01-20</t>
+  </si>
+  <si>
+    <t>2022-02-24</t>
+  </si>
+  <si>
+    <t>2022-02-10</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Energy</t>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
+  </si>
+  <si>
+    <t>Consulting Services</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>REIT - Retail</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Integrated Freight &amp; Logistics</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Agricultural Inputs</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
+    <t>Scientific &amp; Technical Instruments</t>
+  </si>
+  <si>
+    <t>REIT - Industrial</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>REIT - Residential</t>
+  </si>
+  <si>
+    <t>Specialty Retail</t>
   </si>
 </sst>
 </file>
@@ -620,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -741,46 +801,46 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>92.13709677419355</v>
+        <v>96.37096774193549</v>
       </c>
       <c r="C2">
-        <v>408.5</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>135.84</v>
+        <v>361.53</v>
       </c>
       <c r="E2">
-        <v>3.43</v>
+        <v>4.06</v>
       </c>
       <c r="F2">
-        <v>0.09672894653088059</v>
+        <v>2.107082560185682</v>
       </c>
       <c r="G2">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H2">
-        <v>0.1924861969691512</v>
+        <v>2.062750730693223</v>
       </c>
       <c r="I2">
-        <v>127.7480010986328</v>
+        <v>369.5513366699219</v>
       </c>
       <c r="J2">
-        <v>136.98450050354</v>
+        <v>368.6509979248047</v>
       </c>
       <c r="K2">
-        <v>132.6452005004883</v>
+        <v>325.4172006225586</v>
       </c>
       <c r="L2">
-        <v>100.2632502746582</v>
+        <v>249.6318838500977</v>
       </c>
       <c r="M2">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -789,61 +849,61 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T2">
-        <v>7.777777777777777</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>43.9</v>
+        <v>179.83</v>
       </c>
       <c r="Y2">
-        <v>147.67</v>
+        <v>414.5</v>
       </c>
       <c r="Z2">
-        <v>14.07</v>
+        <v>870.86</v>
       </c>
       <c r="AA2">
-        <v>-1685.95</v>
+        <v>-104.17</v>
       </c>
       <c r="AB2">
-        <v>2650</v>
+        <v>298.99</v>
       </c>
       <c r="AC2">
-        <v>233.33</v>
+        <v>440</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>5.95</v>
       </c>
       <c r="AE2">
-        <v>-56.52</v>
+        <v>37.3</v>
       </c>
       <c r="AF2">
-        <v>53.33</v>
+        <v>156.56</v>
       </c>
       <c r="AG2">
-        <v>400</v>
+        <v>53.3</v>
       </c>
       <c r="AH2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="AI2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="AK2">
-        <v>81.15290066997221</v>
+        <v>89.6255099385217</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -851,49 +911,49 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>93.54838709677419</v>
+        <v>97.37903225806451</v>
       </c>
       <c r="C3">
-        <v>267</v>
+        <v>174</v>
       </c>
       <c r="D3">
-        <v>268.49</v>
+        <v>107.56</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="F3">
-        <v>-1.139672336500711</v>
+        <v>0.4860923827528896</v>
       </c>
       <c r="G3">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
-        <v>-1.490793906080917</v>
+        <v>0.8011294886790196</v>
       </c>
       <c r="I3">
-        <v>259.0920043945313</v>
+        <v>108.9120010375977</v>
       </c>
       <c r="J3">
-        <v>257.6425003051758</v>
+        <v>112.216499710083</v>
       </c>
       <c r="K3">
-        <v>253.4827996826172</v>
+        <v>106.5909997558594</v>
       </c>
       <c r="L3">
-        <v>229.1240999603272</v>
+        <v>96.89599988937378</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="N3">
         <v>1.02</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -902,58 +962,58 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>88.69</v>
+        <v>47.94</v>
       </c>
       <c r="Y3">
-        <v>305.66</v>
+        <v>128.81</v>
       </c>
       <c r="Z3">
-        <v>77.09</v>
+        <v>28.68</v>
       </c>
       <c r="AA3">
-        <v>5.44</v>
+        <v>166.14</v>
       </c>
       <c r="AB3">
-        <v>492.36</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="AC3">
-        <v>283.47</v>
+        <v>456.49</v>
       </c>
       <c r="AD3">
-        <v>5.83</v>
+        <v>15.94</v>
       </c>
       <c r="AE3">
-        <v>-2.32</v>
+        <v>44.36</v>
       </c>
       <c r="AF3">
-        <v>465.38</v>
+        <v>62.9</v>
       </c>
       <c r="AG3">
-        <v>-207.44</v>
+        <v>136.64</v>
       </c>
       <c r="AH3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AI3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="AK3">
-        <v>58.48371751464229</v>
+        <v>88.17549857215307</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -961,109 +1021,109 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>92.33870967741935</v>
+        <v>99.19354838709677</v>
       </c>
       <c r="C4">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="D4">
-        <v>64.31999999999999</v>
+        <v>141.24</v>
       </c>
       <c r="E4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="F4">
-        <v>-0.8111181494014071</v>
+        <v>0.01944369531011534</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>-1.041919211934232</v>
+        <v>0.4646971574752317</v>
       </c>
       <c r="I4">
-        <v>63.40399856567383</v>
+        <v>142.6059997558594</v>
       </c>
       <c r="J4">
-        <v>61.23749961853027</v>
+        <v>143.7925010681152</v>
       </c>
       <c r="K4">
-        <v>58.4931999206543</v>
+        <v>133.1518005371094</v>
       </c>
       <c r="L4">
-        <v>49.8431499671936</v>
+        <v>105.1359504699707</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="N4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>21.95</v>
+        <v>61.05</v>
       </c>
       <c r="Y4">
-        <v>65.27</v>
+        <v>149.78</v>
       </c>
       <c r="Z4">
-        <v>41.2</v>
+        <v>84.05</v>
       </c>
       <c r="AA4">
-        <v>0.08</v>
+        <v>40.78</v>
       </c>
       <c r="AB4">
-        <v>207.89</v>
+        <v>231.53</v>
       </c>
       <c r="AC4">
-        <v>421.87</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AD4">
-        <v>9.640000000000001</v>
+        <v>15.41</v>
       </c>
       <c r="AE4">
-        <v>4275</v>
+        <v>6.59</v>
       </c>
       <c r="AF4">
-        <v>87.09999999999999</v>
+        <v>-26.32</v>
       </c>
       <c r="AG4">
-        <v>-196.88</v>
+        <v>118.58</v>
       </c>
       <c r="AH4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AI4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AK4">
-        <v>55.1577415251168</v>
+        <v>76.87270961424117</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1071,43 +1131,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>99.39516129032258</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>37.47</v>
+        <v>41.59</v>
       </c>
       <c r="E5">
-        <v>4.41</v>
+        <v>3.2</v>
       </c>
       <c r="F5">
-        <v>0.9440529027343488</v>
+        <v>1.050982899130984</v>
       </c>
       <c r="G5">
-        <v>3.87</v>
+        <v>3.11</v>
       </c>
       <c r="H5">
-        <v>1.090235585262521</v>
+        <v>1.659031933248678</v>
       </c>
       <c r="I5">
-        <v>35.04800033569336</v>
+        <v>42.22200012207031</v>
       </c>
       <c r="J5">
-        <v>34.86650037765503</v>
+        <v>42.76400032043457</v>
       </c>
       <c r="K5">
-        <v>31.57980010986328</v>
+        <v>40.4578002166748</v>
       </c>
       <c r="L5">
-        <v>20.08705002307892</v>
+        <v>29.60075009346008</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="N5">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1128,52 +1188,52 @@
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>4.82</v>
+        <v>14.34</v>
       </c>
       <c r="Y5">
-        <v>39.1</v>
+        <v>45.56</v>
       </c>
       <c r="Z5">
-        <v>38.02</v>
+        <v>24.11</v>
       </c>
       <c r="AA5">
-        <v>-0.04</v>
+        <v>-0.38</v>
       </c>
       <c r="AB5">
-        <v>180.39</v>
+        <v>119.22</v>
       </c>
       <c r="AC5">
-        <v>247.06</v>
+        <v>559.26</v>
       </c>
       <c r="AD5">
-        <v>4.6</v>
+        <v>9.31</v>
       </c>
       <c r="AE5">
-        <v>127.27</v>
+        <v>226.32</v>
       </c>
       <c r="AF5">
-        <v>633.33</v>
+        <v>15.15</v>
       </c>
       <c r="AG5">
-        <v>108.82</v>
+        <v>222.22</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AI5" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="AK5">
-        <v>48.27163598029622</v>
+        <v>71.06679457401641</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1181,43 +1241,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>95.56451612903226</v>
+        <v>98.79032258064517</v>
       </c>
       <c r="C6">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>38.8</v>
+        <v>19.87</v>
       </c>
       <c r="E6">
-        <v>4.37</v>
+        <v>2.43</v>
       </c>
       <c r="F6">
-        <v>0.9094682514607378</v>
+        <v>0.1054052956285214</v>
       </c>
       <c r="G6">
-        <v>3.11</v>
+        <v>2.53</v>
       </c>
       <c r="H6">
-        <v>0.1426112309528529</v>
+        <v>0.6833781727576935</v>
       </c>
       <c r="I6">
-        <v>37.81600036621094</v>
+        <v>19.6120002746582</v>
       </c>
       <c r="J6">
-        <v>39.71400012969971</v>
+        <v>19.74700012207031</v>
       </c>
       <c r="K6">
-        <v>37.63660011291504</v>
+        <v>17.19020009994507</v>
       </c>
       <c r="L6">
-        <v>27.01785005569458</v>
+        <v>14.20684998989105</v>
       </c>
       <c r="M6">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1238,52 +1298,52 @@
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
       <c r="Y6">
-        <v>42.38</v>
+        <v>20.79</v>
       </c>
       <c r="Z6">
-        <v>13.71</v>
+        <v>57.15</v>
       </c>
       <c r="AA6">
-        <v>33.89</v>
+        <v>5.35</v>
       </c>
       <c r="AB6">
-        <v>16.33</v>
+        <v>196</v>
       </c>
       <c r="AC6">
-        <v>800</v>
+        <v>165.71</v>
       </c>
       <c r="AD6">
-        <v>2.52</v>
+        <v>4.96</v>
       </c>
       <c r="AE6">
-        <v>-46.15</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>53</v>
+        <v>228.57</v>
+      </c>
+      <c r="AF6">
+        <v>-82.93000000000001</v>
       </c>
       <c r="AG6">
-        <v>100</v>
+        <v>217.14</v>
       </c>
       <c r="AH6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AI6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AK6">
-        <v>40.12700442765086</v>
+        <v>70.27807328337438</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1291,49 +1351,49 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.38709677419355</v>
+        <v>98.18548387096774</v>
       </c>
       <c r="C7">
-        <v>443</v>
+        <v>258</v>
       </c>
       <c r="D7">
-        <v>331.76</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E7">
-        <v>5.11</v>
+        <v>2.68</v>
       </c>
       <c r="F7">
-        <v>1.549284300022541</v>
+        <v>0.4124110110513989</v>
       </c>
       <c r="G7">
-        <v>3.76</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>0.9530794287177005</v>
+        <v>-0.1408810386915857</v>
       </c>
       <c r="I7">
-        <v>311.4480041503906</v>
+        <v>71.25200042724609</v>
       </c>
       <c r="J7">
-        <v>328.377001953125</v>
+        <v>69.56699981689454</v>
       </c>
       <c r="K7">
-        <v>285.056198425293</v>
+        <v>61.53959991455078</v>
       </c>
       <c r="L7">
-        <v>203.6288492584229</v>
+        <v>50.44345001220703</v>
       </c>
       <c r="M7">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1342,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1354,46 +1414,46 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>75.5</v>
+        <v>34.42</v>
       </c>
       <c r="Y7">
-        <v>364</v>
+        <v>74.2</v>
       </c>
       <c r="Z7">
-        <v>14.49</v>
+        <v>10.64</v>
       </c>
       <c r="AA7">
-        <v>67.42</v>
+        <v>104.94</v>
       </c>
       <c r="AB7">
-        <v>17.36</v>
+        <v>144.41</v>
       </c>
       <c r="AC7">
-        <v>192.75</v>
+        <v>152.1</v>
       </c>
       <c r="AD7">
-        <v>8.99</v>
+        <v>11.1</v>
       </c>
       <c r="AE7">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AF7">
-        <v>78.84999999999999</v>
+        <v>185.71</v>
       </c>
       <c r="AG7">
-        <v>50.72</v>
+        <v>-29.41</v>
       </c>
       <c r="AH7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AI7" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="AK7">
-        <v>25.5983676829431</v>
+        <v>69.69020793390939</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1401,43 +1461,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>91.12903225806451</v>
+        <v>98.58870967741935</v>
       </c>
       <c r="C8">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="D8">
-        <v>58.95</v>
+        <v>62.54</v>
       </c>
       <c r="E8">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="F8">
-        <v>0.1399597606228941</v>
+        <v>-0.05423767639137533</v>
       </c>
       <c r="G8">
-        <v>3.49</v>
+        <v>2.81</v>
       </c>
       <c r="H8">
-        <v>0.6164234081076873</v>
+        <v>1.154383436442997</v>
       </c>
       <c r="I8">
-        <v>56.12400054931641</v>
+        <v>61.79800033569336</v>
       </c>
       <c r="J8">
-        <v>56.36650047302246</v>
+        <v>60.73350028991699</v>
       </c>
       <c r="K8">
-        <v>55.60420028686524</v>
+        <v>52.28820014953613</v>
       </c>
       <c r="L8">
-        <v>42.22990014076233</v>
+        <v>43.40959995269775</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1449,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1464,46 +1524,46 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>13.71</v>
+        <v>29.03</v>
       </c>
       <c r="Y8">
-        <v>64.05</v>
+        <v>65.47</v>
       </c>
       <c r="Z8">
-        <v>89.40000000000001</v>
+        <v>20.17</v>
       </c>
       <c r="AA8">
-        <v>0.64</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AB8">
-        <v>54.64</v>
+        <v>122.54</v>
       </c>
       <c r="AC8">
-        <v>69.41</v>
+        <v>242.86</v>
       </c>
       <c r="AD8">
-        <v>-7.42</v>
+        <v>7.49</v>
       </c>
       <c r="AE8">
-        <v>16.13</v>
+        <v>67.44</v>
       </c>
       <c r="AF8">
-        <v>39.22</v>
+        <v>95.45</v>
       </c>
       <c r="AG8">
-        <v>40</v>
+        <v>4.76</v>
       </c>
       <c r="AH8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AI8" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="AJ8" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="AK8">
-        <v>24.58426382932166</v>
+        <v>68.73918769416937</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1511,43 +1571,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>96.16935483870968</v>
+        <v>91.33064516129032</v>
       </c>
       <c r="C9">
-        <v>353</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>87.41</v>
+        <v>37.64</v>
       </c>
       <c r="E9">
-        <v>1.77</v>
+        <v>2.76</v>
       </c>
       <c r="F9">
-        <v>-1.338534081323974</v>
+        <v>0.5106528399867193</v>
       </c>
       <c r="G9">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="H9">
-        <v>-0.9172317968934864</v>
+        <v>0.4142323077946639</v>
       </c>
       <c r="I9">
-        <v>84.51800079345703</v>
+        <v>35.97799987792969</v>
       </c>
       <c r="J9">
-        <v>81.26100044250488</v>
+        <v>32.87399997711181</v>
       </c>
       <c r="K9">
-        <v>77.32740020751953</v>
+        <v>30.43559989929199</v>
       </c>
       <c r="L9">
-        <v>59.12845010757447</v>
+        <v>30.34584995269775</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1571,49 +1631,49 @@
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>23.77</v>
+        <v>22.76</v>
       </c>
       <c r="Y9">
-        <v>88.25</v>
+        <v>38.38</v>
       </c>
       <c r="Z9">
-        <v>10.46</v>
+        <v>37</v>
       </c>
       <c r="AA9">
-        <v>21.3</v>
+        <v>33.4</v>
       </c>
       <c r="AB9">
-        <v>3.96</v>
+        <v>91.84</v>
       </c>
       <c r="AC9">
-        <v>340.74</v>
+        <v>218.07</v>
       </c>
       <c r="AD9">
-        <v>3.95</v>
+        <v>-190.82</v>
       </c>
       <c r="AE9">
-        <v>2.59</v>
+        <v>180.85</v>
       </c>
       <c r="AF9">
-        <v>118.87</v>
+        <v>-6</v>
       </c>
       <c r="AG9">
-        <v>96.3</v>
+        <v>20.48</v>
       </c>
       <c r="AH9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AI9" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AK9">
-        <v>20.14974692878014</v>
+        <v>63.61738870782229</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1621,43 +1681,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>95.36290322580645</v>
+        <v>90.92741935483872</v>
       </c>
       <c r="C10">
-        <v>140</v>
+        <v>487</v>
       </c>
       <c r="D10">
-        <v>25.73</v>
+        <v>556.7</v>
       </c>
       <c r="E10">
-        <v>2.21</v>
+        <v>1.69</v>
       </c>
       <c r="F10">
-        <v>-0.9581029173142536</v>
+        <v>-0.8033316220231963</v>
       </c>
       <c r="G10">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="H10">
-        <v>-1.353637749536097</v>
+        <v>-0.5950646858166989</v>
       </c>
       <c r="I10">
-        <v>24.94200019836426</v>
+        <v>556.4659912109375</v>
       </c>
       <c r="J10">
-        <v>23.80850019454956</v>
+        <v>554.0894958496094</v>
       </c>
       <c r="K10">
-        <v>21.10040012359619</v>
+        <v>503.0629962158203</v>
       </c>
       <c r="L10">
-        <v>16.15115002632141</v>
+        <v>445.1352989196777</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1669,61 +1729,61 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>7.9</v>
+        <v>305.47</v>
       </c>
       <c r="Y10">
-        <v>25.85</v>
+        <v>582.27</v>
       </c>
       <c r="Z10">
-        <v>10.65</v>
+        <v>17.68</v>
       </c>
       <c r="AA10">
-        <v>138.94</v>
+        <v>22.74</v>
       </c>
       <c r="AB10">
-        <v>4.55</v>
+        <v>56.2</v>
       </c>
       <c r="AC10">
-        <v>131.45</v>
+        <v>215.07</v>
       </c>
       <c r="AD10">
-        <v>2.88</v>
+        <v>18.74</v>
       </c>
       <c r="AE10">
-        <v>550</v>
+        <v>-28.9</v>
       </c>
       <c r="AF10">
-        <v>108.82</v>
+        <v>164.08</v>
       </c>
       <c r="AG10">
-        <v>45.16</v>
+        <v>67.81</v>
       </c>
       <c r="AH10" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AI10" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AK10">
-        <v>19.66503645333481</v>
+        <v>58.38186512141539</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1731,46 +1791,46 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>90.7258064516129</v>
+        <v>99.39516129032258</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>117.19</v>
+        <v>32.13</v>
       </c>
       <c r="E11">
-        <v>4.71</v>
+        <v>4.29</v>
       </c>
       <c r="F11">
-        <v>1.203437787286431</v>
+        <v>2.38952781837473</v>
       </c>
       <c r="G11">
-        <v>3.57</v>
+        <v>3.05</v>
       </c>
       <c r="H11">
-        <v>0.7161733401402834</v>
+        <v>1.558102233887541</v>
       </c>
       <c r="I11">
-        <v>112.6440002441406</v>
+        <v>32.22319946289063</v>
       </c>
       <c r="J11">
-        <v>115.4799999237061</v>
+        <v>31.14469976425171</v>
       </c>
       <c r="K11">
-        <v>105.9404000854492</v>
+        <v>25.88387985229492</v>
       </c>
       <c r="L11">
-        <v>75.93495021820068</v>
+        <v>19.42917497634888</v>
       </c>
       <c r="M11">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1779,61 +1839,61 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>0.5555555555555555</v>
+        <v>10</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>36.64</v>
+        <v>11.57</v>
       </c>
       <c r="Y11">
-        <v>124.5</v>
+        <v>34.65</v>
       </c>
       <c r="Z11">
-        <v>89.43000000000001</v>
+        <v>648.89</v>
       </c>
       <c r="AA11">
-        <v>43.58</v>
+        <v>875.84</v>
       </c>
       <c r="AB11">
-        <v>8.789999999999999</v>
+        <v>53.67</v>
       </c>
       <c r="AC11">
-        <v>50</v>
+        <v>65.83</v>
       </c>
       <c r="AD11">
-        <v>9.85</v>
+        <v>10.35</v>
       </c>
       <c r="AE11">
-        <v>-0.8100000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="AF11">
-        <v>34.78</v>
+        <v>23.38</v>
       </c>
       <c r="AG11">
-        <v>12.2</v>
+        <v>28.98</v>
       </c>
       <c r="AH11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AI11" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AK11">
-        <v>6.668092243314866</v>
+        <v>56.65073349055587</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1841,46 +1901,46 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>91.33064516129032</v>
+        <v>91.12903225806451</v>
       </c>
       <c r="C12">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="D12">
-        <v>83.25</v>
+        <v>250.39</v>
       </c>
       <c r="E12">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="F12">
-        <v>-1.494165012055223</v>
+        <v>-1.196298937764479</v>
       </c>
       <c r="G12">
-        <v>1.93</v>
+        <v>1.13</v>
       </c>
       <c r="H12">
-        <v>-1.328700266527947</v>
+        <v>-1.671648145668819</v>
       </c>
       <c r="I12">
-        <v>81.83199920654297</v>
+        <v>247.3179992675781</v>
       </c>
       <c r="J12">
-        <v>78.65100021362305</v>
+        <v>242.9510009765625</v>
       </c>
       <c r="K12">
-        <v>74.84979965209961</v>
+        <v>227.6596008300781</v>
       </c>
       <c r="L12">
-        <v>58.08720003128052</v>
+        <v>201.1198503112793</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>1.09</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -1892,58 +1952,58 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="U12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>27.2</v>
+        <v>149.31</v>
       </c>
       <c r="Y12">
-        <v>83.81</v>
+        <v>256.39</v>
       </c>
       <c r="Z12">
-        <v>111.29</v>
+        <v>161.8</v>
       </c>
       <c r="AA12">
-        <v>10.51</v>
+        <v>18.8</v>
       </c>
       <c r="AB12">
-        <v>4.3</v>
+        <v>37.04</v>
       </c>
       <c r="AC12">
-        <v>83.33</v>
+        <v>102.96</v>
       </c>
       <c r="AD12">
-        <v>3.63</v>
+        <v>-120.3</v>
       </c>
       <c r="AE12">
-        <v>11.31</v>
+        <v>-35.83</v>
       </c>
       <c r="AF12">
-        <v>-15.15</v>
+        <v>32.61</v>
       </c>
       <c r="AG12">
-        <v>94.12</v>
+        <v>138.52</v>
       </c>
       <c r="AH12" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AI12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AK12">
-        <v>5.907753681659235</v>
+        <v>53.19495176839168</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1951,40 +2011,40 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>97.17741935483872</v>
+        <v>93.54838709677419</v>
       </c>
       <c r="C13">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="D13">
-        <v>33.45</v>
+        <v>105.11</v>
       </c>
       <c r="E13">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="F13">
-        <v>1.021868368099973</v>
+        <v>0.04400415254394557</v>
       </c>
       <c r="G13">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="H13">
-        <v>0.4917359930669414</v>
+        <v>0.262837758752959</v>
       </c>
       <c r="I13">
-        <v>31.61200065612793</v>
+        <v>102.8599990844727</v>
       </c>
       <c r="J13">
-        <v>30.37950010299683</v>
+        <v>101.6120006561279</v>
       </c>
       <c r="K13">
-        <v>28.29919994354248</v>
+        <v>91.48460037231445</v>
       </c>
       <c r="L13">
-        <v>20.02829996109009</v>
+        <v>87.3549500656128</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
         <v>1.12</v>
@@ -2014,46 +2074,46 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>6.5</v>
+        <v>58.04</v>
       </c>
       <c r="Y13">
-        <v>34.11</v>
+        <v>116.93</v>
       </c>
       <c r="Z13">
-        <v>8.77</v>
+        <v>19.06</v>
       </c>
       <c r="AA13">
-        <v>2.84</v>
+        <v>26.51</v>
       </c>
       <c r="AB13">
-        <v>153.01</v>
+        <v>35.9</v>
       </c>
       <c r="AC13">
-        <v>505.56</v>
+        <v>108.04</v>
       </c>
       <c r="AD13">
-        <v>8.49</v>
+        <v>87.52</v>
       </c>
       <c r="AE13">
-        <v>11050</v>
+        <v>14.78</v>
       </c>
       <c r="AF13">
-        <v>-115.38</v>
+        <v>43.97</v>
       </c>
       <c r="AG13">
-        <v>124.07</v>
+        <v>25.89</v>
       </c>
       <c r="AH13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AI13" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK13">
-        <v>54.40176005584486</v>
+        <v>50.28826381118895</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2061,43 +2121,43 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>93.95161290322581</v>
+        <v>94.55645161290323</v>
       </c>
       <c r="C14">
-        <v>304</v>
+        <v>436</v>
       </c>
       <c r="D14">
-        <v>47.05</v>
+        <v>291</v>
       </c>
       <c r="E14">
-        <v>2.86</v>
+        <v>2.03</v>
       </c>
       <c r="F14">
-        <v>-0.3961023341180757</v>
+        <v>-0.3858038490480831</v>
       </c>
       <c r="G14">
-        <v>2.73</v>
+        <v>1.84</v>
       </c>
       <c r="H14">
-        <v>-0.331200946201981</v>
+        <v>-0.4773133698953732</v>
       </c>
       <c r="I14">
-        <v>45.36000061035156</v>
+        <v>281.8019958496094</v>
       </c>
       <c r="J14">
-        <v>43.05200004577637</v>
+        <v>283.8154983520508</v>
       </c>
       <c r="K14">
-        <v>41.72239990234375</v>
+        <v>272.0761978149414</v>
       </c>
       <c r="L14">
-        <v>32.54264991760254</v>
+        <v>238.8287991333008</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="N14">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2115,55 +2175,55 @@
         <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>161.87</v>
       </c>
       <c r="Y14">
-        <v>47.5</v>
+        <v>292.11</v>
       </c>
       <c r="Z14">
-        <v>4.81</v>
+        <v>31.35</v>
       </c>
       <c r="AA14">
-        <v>-392.99</v>
+        <v>4.52</v>
       </c>
       <c r="AB14">
-        <v>34.5</v>
+        <v>27.68</v>
       </c>
       <c r="AC14">
-        <v>1387.5</v>
+        <v>175.41</v>
       </c>
       <c r="AD14">
-        <v>12.14</v>
+        <v>5.81</v>
       </c>
       <c r="AE14">
-        <v>60.81</v>
+        <v>-5.08</v>
       </c>
       <c r="AF14">
-        <v>8.82</v>
+        <v>6.63</v>
       </c>
       <c r="AG14">
-        <v>750</v>
+        <v>172.13</v>
       </c>
       <c r="AH14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="AI14" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AK14">
-        <v>52.23325041129666</v>
+        <v>50.00399644180958</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2171,61 +2231,61 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>96.9758064516129</v>
+        <v>94.35483870967742</v>
       </c>
       <c r="C15">
-        <v>109</v>
+        <v>335</v>
       </c>
       <c r="D15">
-        <v>19.44</v>
+        <v>178.52</v>
       </c>
       <c r="E15">
-        <v>3.42</v>
+        <v>1.42</v>
       </c>
       <c r="F15">
-        <v>0.08808278371247764</v>
+        <v>-1.134897794679904</v>
       </c>
       <c r="G15">
-        <v>3.76</v>
+        <v>1.45</v>
       </c>
       <c r="H15">
-        <v>0.9530794287177005</v>
+        <v>-1.133356415742759</v>
       </c>
       <c r="I15">
-        <v>18.2560001373291</v>
+        <v>177.1920013427734</v>
       </c>
       <c r="J15">
-        <v>18.14900007247925</v>
+        <v>177.1272506713867</v>
       </c>
       <c r="K15">
-        <v>16.81020002365112</v>
+        <v>163.0741009521484</v>
       </c>
       <c r="L15">
-        <v>15.01084997653961</v>
+        <v>137.4688752746582</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="N15">
         <v>1.09</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15">
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2234,46 +2294,46 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>5.63</v>
+        <v>94.72</v>
       </c>
       <c r="Y15">
-        <v>19.69</v>
+        <v>182.41</v>
       </c>
       <c r="Z15">
-        <v>3.48</v>
+        <v>33.22</v>
       </c>
       <c r="AA15">
-        <v>-211.11</v>
+        <v>37.62</v>
       </c>
       <c r="AB15">
-        <v>30.15</v>
+        <v>17.66</v>
       </c>
       <c r="AC15">
-        <v>135.38</v>
+        <v>54.04</v>
       </c>
       <c r="AD15">
-        <v>0.6899999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AE15">
-        <v>109.79</v>
+        <v>6.44</v>
       </c>
       <c r="AF15">
-        <v>-128.16</v>
+        <v>36.26</v>
       </c>
       <c r="AG15">
-        <v>-58.46</v>
+        <v>6.21</v>
       </c>
       <c r="AH15" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="AI15" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AK15">
-        <v>26.50787089045216</v>
+        <v>46.52145838311669</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2281,43 +2341,43 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>95.96774193548387</v>
+        <v>94.15322580645162</v>
       </c>
       <c r="C16">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="D16">
-        <v>21.89</v>
+        <v>151.86</v>
       </c>
       <c r="E16">
-        <v>4.35</v>
+        <v>2.14</v>
       </c>
       <c r="F16">
-        <v>0.892175925823932</v>
+        <v>-0.2507213342620166</v>
       </c>
       <c r="G16">
-        <v>4.34</v>
+        <v>1.98</v>
       </c>
       <c r="H16">
-        <v>1.676266435954026</v>
+        <v>-0.241810738052722</v>
       </c>
       <c r="I16">
-        <v>22.30799980163574</v>
+        <v>154.5679992675781</v>
       </c>
       <c r="J16">
-        <v>19.91649980545044</v>
+        <v>163.9480010986328</v>
       </c>
       <c r="K16">
-        <v>17.73639987945556</v>
+        <v>149.7206005859375</v>
       </c>
       <c r="L16">
-        <v>14.03964998245239</v>
+        <v>130.7889999008179</v>
       </c>
       <c r="M16">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N16">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2338,52 +2398,52 @@
         <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>3.8</v>
+        <v>82.02</v>
       </c>
       <c r="Y16">
-        <v>23.85</v>
+        <v>171.12</v>
       </c>
       <c r="Z16">
-        <v>5.36</v>
+        <v>42.71</v>
       </c>
       <c r="AA16">
-        <v>0.32</v>
+        <v>2.42</v>
       </c>
       <c r="AB16">
-        <v>39.6</v>
+        <v>17.33</v>
       </c>
       <c r="AC16">
-        <v>100.25</v>
+        <v>143.53</v>
       </c>
       <c r="AD16">
-        <v>-8.529999999999999</v>
+        <v>20.32</v>
       </c>
       <c r="AE16">
-        <v>400</v>
+        <v>10.11</v>
       </c>
       <c r="AF16">
-        <v>99.02</v>
+        <v>38.24</v>
       </c>
       <c r="AG16">
-        <v>91.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AI16" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AJ16" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AK16">
-        <v>25.6727817153164</v>
+        <v>44.23243186983956</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2391,109 +2451,989 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>93.14516129032258</v>
+        <v>93.75</v>
       </c>
       <c r="C17">
-        <v>321</v>
+        <v>68</v>
       </c>
       <c r="D17">
-        <v>34.44</v>
+        <v>146.49</v>
       </c>
       <c r="E17">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>-0.7073641955805742</v>
+        <v>0.805378326792682</v>
       </c>
       <c r="G17">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="H17">
-        <v>-0.3686071707142045</v>
+        <v>0.4142323077946639</v>
       </c>
       <c r="I17">
-        <v>34.21999969482422</v>
+        <v>147.9720001220703</v>
       </c>
       <c r="J17">
-        <v>32.03899984359741</v>
+        <v>151.9004997253418</v>
       </c>
       <c r="K17">
-        <v>30.17779991149902</v>
+        <v>140.6002000427246</v>
       </c>
       <c r="L17">
-        <v>22.16369998931885</v>
+        <v>133.8868500900269</v>
       </c>
       <c r="M17">
+        <v>0.97</v>
+      </c>
+      <c r="N17">
+        <v>1.05</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>83.53</v>
+      </c>
+      <c r="Y17">
+        <v>159</v>
+      </c>
+      <c r="Z17">
+        <v>125.58</v>
+      </c>
+      <c r="AA17">
+        <v>26.49</v>
+      </c>
+      <c r="AB17">
+        <v>24.9</v>
+      </c>
+      <c r="AC17">
+        <v>54.47</v>
+      </c>
+      <c r="AD17">
+        <v>13.98</v>
+      </c>
+      <c r="AE17">
+        <v>0.53</v>
+      </c>
+      <c r="AF17">
+        <v>30.34</v>
+      </c>
+      <c r="AG17">
+        <v>17.89</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK17">
+        <v>43.39119971768306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18">
+        <v>91.53225806451613</v>
+      </c>
+      <c r="C18">
+        <v>109</v>
+      </c>
+      <c r="D18">
+        <v>43.94</v>
+      </c>
+      <c r="E18">
+        <v>1.91</v>
+      </c>
+      <c r="F18">
+        <v>-0.5331665924510641</v>
+      </c>
+      <c r="G18">
+        <v>1.93</v>
+      </c>
+      <c r="H18">
+        <v>-0.325918820853669</v>
+      </c>
+      <c r="I18">
+        <v>42.66000061035156</v>
+      </c>
+      <c r="J18">
+        <v>43.85949993133545</v>
+      </c>
+      <c r="K18">
+        <v>43.80020004272461</v>
+      </c>
+      <c r="L18">
+        <v>39.88829996109009</v>
+      </c>
+      <c r="M18">
+        <v>0.97</v>
+      </c>
+      <c r="N18">
+        <v>0.97</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>26.34</v>
+      </c>
+      <c r="Y18">
+        <v>45.92</v>
+      </c>
+      <c r="Z18">
+        <v>29.97</v>
+      </c>
+      <c r="AA18">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="AB18">
+        <v>31.18</v>
+      </c>
+      <c r="AC18">
+        <v>24.05</v>
+      </c>
+      <c r="AD18">
+        <v>3.45</v>
+      </c>
+      <c r="AE18">
+        <v>3.16</v>
+      </c>
+      <c r="AF18">
+        <v>1.06</v>
+      </c>
+      <c r="AG18">
+        <v>18.99</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK18">
+        <v>41.47818249201391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>96.16935483870968</v>
+      </c>
+      <c r="C19">
+        <v>227</v>
+      </c>
+      <c r="D19">
+        <v>672.12</v>
+      </c>
+      <c r="E19">
+        <v>3.39</v>
+      </c>
+      <c r="F19">
+        <v>1.284307242852371</v>
+      </c>
+      <c r="G19">
+        <v>2.32</v>
+      </c>
+      <c r="H19">
+        <v>0.3301242249937166</v>
+      </c>
+      <c r="I19">
+        <v>669.9759887695312</v>
+      </c>
+      <c r="J19">
+        <v>645.0459991455078</v>
+      </c>
+      <c r="K19">
+        <v>598.7389953613281</v>
+      </c>
+      <c r="L19">
+        <v>498.2352479553223</v>
+      </c>
+      <c r="M19">
+        <v>1.04</v>
+      </c>
+      <c r="N19">
+        <v>1.12</v>
+      </c>
+      <c r="P19">
+        <v>7</v>
+      </c>
+      <c r="Q19">
+        <v>4</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>353.47</v>
+      </c>
+      <c r="Y19">
+        <v>716.86</v>
+      </c>
+      <c r="Z19">
+        <v>173.4</v>
+      </c>
+      <c r="AA19">
+        <v>10.89</v>
+      </c>
+      <c r="AB19">
+        <v>1.98</v>
+      </c>
+      <c r="AC19">
+        <v>1100</v>
+      </c>
+      <c r="AD19">
+        <v>2.34</v>
+      </c>
+      <c r="AE19">
+        <v>-42.86</v>
+      </c>
+      <c r="AF19">
+        <v>-72.56999999999999</v>
+      </c>
+      <c r="AG19">
+        <v>7557.14</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK19">
+        <v>38.84615384615384</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>90.32258064516128</v>
+      </c>
+      <c r="C20">
+        <v>342</v>
+      </c>
+      <c r="D20">
+        <v>198.48</v>
+      </c>
+      <c r="E20">
+        <v>1.78</v>
+      </c>
+      <c r="F20">
+        <v>-0.6928095644709603</v>
+      </c>
+      <c r="G20">
+        <v>1.55</v>
+      </c>
+      <c r="H20">
+        <v>-0.9651402501408651</v>
+      </c>
+      <c r="I20">
+        <v>195.147998046875</v>
+      </c>
+      <c r="J20">
+        <v>191.2324996948242</v>
+      </c>
+      <c r="K20">
+        <v>179.4655999755859</v>
+      </c>
+      <c r="L20">
+        <v>159.1486996459961</v>
+      </c>
+      <c r="M20">
+        <v>1.02</v>
+      </c>
+      <c r="N20">
+        <v>1.09</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>121.63</v>
+      </c>
+      <c r="Y20">
+        <v>200.76</v>
+      </c>
+      <c r="Z20">
+        <v>33.66</v>
+      </c>
+      <c r="AA20">
+        <v>14.21</v>
+      </c>
+      <c r="AB20">
+        <v>13.08</v>
+      </c>
+      <c r="AC20">
+        <v>63.44</v>
+      </c>
+      <c r="AD20">
+        <v>7.45</v>
+      </c>
+      <c r="AE20">
+        <v>10.14</v>
+      </c>
+      <c r="AF20">
+        <v>36.63</v>
+      </c>
+      <c r="AG20">
+        <v>8.6</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK20">
+        <v>37.63840637103383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21">
+        <v>95.76612903225806</v>
+      </c>
+      <c r="C21">
+        <v>374</v>
+      </c>
+      <c r="D21">
+        <v>205.41</v>
+      </c>
+      <c r="E21">
+        <v>1.44</v>
+      </c>
+      <c r="F21">
+        <v>-1.110337337446074</v>
+      </c>
+      <c r="G21">
+        <v>1.52</v>
+      </c>
+      <c r="H21">
+        <v>-1.015605099821433</v>
+      </c>
+      <c r="I21">
+        <v>201.3579986572266</v>
+      </c>
+      <c r="J21">
+        <v>199.9485000610352</v>
+      </c>
+      <c r="K21">
+        <v>188.3403997802734</v>
+      </c>
+      <c r="L21">
+        <v>164.2965997695923</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
         <v>1.07</v>
       </c>
-      <c r="N17">
-        <v>1.13</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-      <c r="X17">
-        <v>3.66</v>
-      </c>
-      <c r="Y17">
-        <v>35.27</v>
-      </c>
-      <c r="Z17">
-        <v>6.13</v>
-      </c>
-      <c r="AA17">
-        <v>-136.86</v>
-      </c>
-      <c r="AB17">
-        <v>19.69</v>
-      </c>
-      <c r="AC17">
-        <v>99.61</v>
-      </c>
-      <c r="AD17">
-        <v>2.47</v>
-      </c>
-      <c r="AE17">
-        <v>-118.75</v>
-      </c>
-      <c r="AF17">
-        <v>-23.81</v>
-      </c>
-      <c r="AG17">
-        <v>102.76</v>
-      </c>
-      <c r="AH17" t="s">
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>106.56</v>
+      </c>
+      <c r="Y21">
+        <v>207.56</v>
+      </c>
+      <c r="Z21">
+        <v>23.59</v>
+      </c>
+      <c r="AA21">
+        <v>12.04</v>
+      </c>
+      <c r="AB21">
+        <v>17.47</v>
+      </c>
+      <c r="AC21">
+        <v>19.49</v>
+      </c>
+      <c r="AD21">
+        <v>5.91</v>
+      </c>
+      <c r="AE21">
+        <v>12.8</v>
+      </c>
+      <c r="AF21">
+        <v>-18.83</v>
+      </c>
+      <c r="AG21">
+        <v>30.51</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK21">
+        <v>34.80780143214047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>93.95161290322581</v>
+      </c>
+      <c r="C22">
+        <v>481</v>
+      </c>
+      <c r="D22">
+        <v>554.46</v>
+      </c>
+      <c r="E22">
+        <v>2.22</v>
+      </c>
+      <c r="F22">
+        <v>-0.1524795053266957</v>
+      </c>
+      <c r="G22">
+        <v>1.98</v>
+      </c>
+      <c r="H22">
+        <v>-0.241810738052722</v>
+      </c>
+      <c r="I22">
+        <v>552.4920166015625</v>
+      </c>
+      <c r="J22">
+        <v>554.4945068359375</v>
+      </c>
+      <c r="K22">
+        <v>520.6908044433594</v>
+      </c>
+      <c r="L22">
+        <v>422.090350189209</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1.06</v>
+      </c>
+      <c r="P22">
+        <v>4</v>
+      </c>
+      <c r="Q22">
+        <v>9</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>12.22222222222222</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>301.51</v>
+      </c>
+      <c r="Y22">
+        <v>580</v>
+      </c>
+      <c r="Z22">
+        <v>23.19</v>
+      </c>
+      <c r="AA22">
+        <v>38.3</v>
+      </c>
+      <c r="AB22">
+        <v>5.43</v>
+      </c>
+      <c r="AC22">
+        <v>56.25</v>
+      </c>
+      <c r="AD22">
+        <v>5.91</v>
+      </c>
+      <c r="AE22">
+        <v>25</v>
+      </c>
+      <c r="AF22">
+        <v>20</v>
+      </c>
+      <c r="AG22">
+        <v>4.17</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK22">
+        <v>34.07068662232171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23">
+        <v>90.12096774193549</v>
+      </c>
+      <c r="C23">
+        <v>485</v>
+      </c>
+      <c r="D23">
+        <v>596.96</v>
+      </c>
+      <c r="E23">
+        <v>1.8</v>
+      </c>
+      <c r="F23">
+        <v>-0.66824910723713</v>
+      </c>
+      <c r="G23">
+        <v>1.87</v>
+      </c>
+      <c r="H23">
+        <v>-0.426848520214805</v>
+      </c>
+      <c r="I23">
+        <v>592.9380126953125</v>
+      </c>
+      <c r="J23">
+        <v>596.293002319336</v>
+      </c>
+      <c r="K23">
+        <v>553.8714019775391</v>
+      </c>
+      <c r="L23">
+        <v>527.1258001708984</v>
+      </c>
+      <c r="M23">
+        <v>0.99</v>
+      </c>
+      <c r="N23">
+        <v>1.07</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>363</v>
+      </c>
+      <c r="Y23">
+        <v>614.1</v>
+      </c>
+      <c r="Z23">
+        <v>27.76</v>
+      </c>
+      <c r="AA23">
+        <v>-31.25</v>
+      </c>
+      <c r="AB23">
+        <v>25.7</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>7.07</v>
+      </c>
+      <c r="AE23">
+        <v>-9.27</v>
+      </c>
+      <c r="AF23">
+        <v>-3.76</v>
+      </c>
+      <c r="AG23">
+        <v>14.52</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK23">
+        <v>23.391488677355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>92.33870967741935</v>
+      </c>
+      <c r="C24">
+        <v>393</v>
+      </c>
+      <c r="D24">
+        <v>207.96</v>
+      </c>
+      <c r="E24">
+        <v>1.71</v>
+      </c>
+      <c r="F24">
+        <v>-0.7787711647893661</v>
+      </c>
+      <c r="G24">
+        <v>1.28</v>
+      </c>
+      <c r="H24">
+        <v>-1.419323897265978</v>
+      </c>
+      <c r="I24">
+        <v>205.8240020751953</v>
+      </c>
+      <c r="J24">
+        <v>204.3934997558594</v>
+      </c>
+      <c r="K24">
+        <v>199.2579998779297</v>
+      </c>
+      <c r="L24">
+        <v>174.7604499816894</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>1.03</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>119.21</v>
+      </c>
+      <c r="Y24">
+        <v>211.97</v>
+      </c>
+      <c r="Z24">
+        <v>21.52</v>
+      </c>
+      <c r="AA24">
+        <v>7.02</v>
+      </c>
+      <c r="AB24">
+        <v>6.27</v>
+      </c>
+      <c r="AC24">
+        <v>1.39</v>
+      </c>
+      <c r="AD24">
+        <v>1.43</v>
+      </c>
+      <c r="AE24">
+        <v>-61.17</v>
+      </c>
+      <c r="AF24">
+        <v>370</v>
+      </c>
+      <c r="AG24">
+        <v>-44.44</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK24">
+        <v>13.86779901472158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
         <v>60</v>
       </c>
-      <c r="AI17" t="s">
-        <v>68</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK17">
-        <v>19.70292591738247</v>
+      <c r="B25">
+        <v>91.93548387096774</v>
+      </c>
+      <c r="C25">
+        <v>165</v>
+      </c>
+      <c r="D25">
+        <v>45.53</v>
+      </c>
+      <c r="E25">
+        <v>1.16</v>
+      </c>
+      <c r="F25">
+        <v>-1.454183738719697</v>
+      </c>
+      <c r="G25">
+        <v>1.44</v>
+      </c>
+      <c r="H25">
+        <v>-1.150178032302948</v>
+      </c>
+      <c r="I25">
+        <v>45.27840042114258</v>
+      </c>
+      <c r="J25">
+        <v>44.87590007781982</v>
+      </c>
+      <c r="K25">
+        <v>42.49331985473633</v>
+      </c>
+      <c r="L25">
+        <v>38.17151993751526</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.07</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>26.72</v>
+      </c>
+      <c r="Y25">
+        <v>46.49</v>
+      </c>
+      <c r="Z25">
+        <v>4.67</v>
+      </c>
+      <c r="AA25">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB25">
+        <v>3</v>
+      </c>
+      <c r="AC25">
+        <v>68.97</v>
+      </c>
+      <c r="AD25">
+        <v>11.1</v>
+      </c>
+      <c r="AE25">
+        <v>-38.94</v>
+      </c>
+      <c r="AF25">
+        <v>105.77</v>
+      </c>
+      <c r="AG25">
+        <v>34.48</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK25">
+        <v>24.88136266458953</v>
       </c>
     </row>
   </sheetData>
